--- a/artfynd/A 54154-2023 artfynd.xlsx
+++ b/artfynd/A 54154-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120723658</v>
+        <v>120723661</v>
       </c>
       <c r="B2" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510836</v>
+        <v>510843</v>
       </c>
       <c r="R2" t="n">
-        <v>6703281</v>
+        <v>6703260</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,16 +775,11 @@
         <v>120723662</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120723661</v>
+        <v>120723658</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510843</v>
+        <v>510836</v>
       </c>
       <c r="R4" t="n">
-        <v>6703260</v>
+        <v>6703281</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,6 +963,113 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>75200653</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lortån S om 3, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>510822</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6703316</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-12-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-12-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54154-2023 artfynd.xlsx
+++ b/artfynd/A 54154-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120723661</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120723662</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120723658</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,8 +1090,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75200653</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>